--- a/WGRDBESstockCoord/format/CEF_issues/counts_mandatory.xlsx
+++ b/WGRDBESstockCoord/format/CEF_issues/counts_mandatory.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/CEF_issues/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{74666AA2-EEC8-48E2-81DB-A0BA6E680777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{115D345F-57D3-4749-8190-E393D97EC8A3}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{E02EFAED-1830-484F-A16C-64F57909150A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE06C13B-299A-4E38-A818-4C383D185A03}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{E9EDB1D5-AC8B-401D-A7AA-35A6E4ABEA11}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{E9EDB1D5-AC8B-401D-A7AA-35A6E4ABEA11}"/>
   </bookViews>
   <sheets>
     <sheet name="dataBasis" sheetId="1" r:id="rId1"/>
     <sheet name="sample_size_y_n" sheetId="2" r:id="rId2"/>
-    <sheet name="input_y_n" sheetId="3" r:id="rId3"/>
+    <sheet name="WGInput" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="61">
   <si>
     <t>no</t>
   </si>
@@ -181,22 +181,49 @@
     <t>Example with official used as input to stock assessement</t>
   </si>
   <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>InterCatchImport</t>
+  </si>
+  <si>
+    <t>Example with estimated discard</t>
+  </si>
+  <si>
+    <t>estimated</t>
+  </si>
+  <si>
+    <t>used_for_WG</t>
+  </si>
+  <si>
+    <t>This column has the same name, but the meaning has changed</t>
+  </si>
+  <si>
+    <t>We need a better word for this</t>
+  </si>
+  <si>
+    <t>WGInput</t>
+  </si>
+  <si>
+    <t>Change to NotApplicable</t>
+  </si>
+  <si>
+    <t>Not a good solution, since it very close to have counts optional and it is not adding any new information</t>
+  </si>
+  <si>
+    <t>We would need new codes in DataBasis</t>
+  </si>
+  <si>
+    <t>originType and dataBasis are very similar</t>
+  </si>
+  <si>
     <t>dataBasis</t>
   </si>
   <si>
-    <t>input_tostockassessment</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>InterCatchImport</t>
-  </si>
-  <si>
-    <t>?</t>
+    <t>This could work, but is will require changes in the upload facilities and functions</t>
   </si>
 </sst>
 </file>
@@ -218,7 +245,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,6 +264,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -250,12 +295,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -271,6 +318,104 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>528512</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>91762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D6F65F-FF13-8562-A39E-BCE8A026C9E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1114425" y="3438525"/>
+          <a:ext cx="9548687" cy="3711262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>292285</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>133738</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A81EA6CD-2BE5-413A-B437-C5E58515A3A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8763000" y="4343400"/>
+          <a:ext cx="9457240" cy="4480948"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,241 +735,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71AB4692-AFD9-4E67-B32D-594941B22D92}">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="3" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>2023</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>15</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3" s="3" t="s">
+      <c r="V3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>2023</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" t="s">
         <v>35</v>
       </c>
-      <c r="T4" s="1">
+      <c r="T4">
         <v>523</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>40</v>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -890,490 +1034,770 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="O8" t="s">
         <v>14</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="T8" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="U8" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="V8" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="W8" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="X8" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Y8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+    <row r="9" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>2023</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="Q9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" s="2">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>2023</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>48</v>
+      </c>
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T10">
+        <v>523</v>
+      </c>
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2023</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T11" s="2">
+        <v>15</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R14" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" t="s">
+        <v>17</v>
+      </c>
+      <c r="T14" t="s">
+        <v>18</v>
+      </c>
+      <c r="U14" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" t="s">
+        <v>20</v>
+      </c>
+      <c r="W14" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2023</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" s="2">
+        <v>15</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16">
+        <v>2023</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>42</v>
+      </c>
+      <c r="R16" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" t="s">
+        <v>35</v>
+      </c>
+      <c r="T16">
+        <v>523</v>
+      </c>
+      <c r="V16" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2023</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="R17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T17" s="4">
         <v>15</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T10" s="1">
-        <v>523</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3">
-        <v>2023</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T11" s="3">
-        <v>15</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>36</v>
+      <c r="V17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="N22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="N23" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDDD92C-0007-472B-9E32-FAD896FF24DF}">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="3" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>2023</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>15</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="V3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>2023</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" s="1" t="s">
+      <c r="Q4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" t="s">
         <v>35</v>
       </c>
-      <c r="T4" s="1">
+      <c r="T4">
         <v>523</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>40</v>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1417,7 +1841,7 @@
         <v>39</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>34</v>
@@ -1438,273 +1862,545 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="O8" t="s">
         <v>14</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="Q8" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="T8" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="U8" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="V8" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="W8" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="X8" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Y8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+    <row r="9" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>2023</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="Q9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="2">
         <v>15</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="V9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>2</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>2023</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>30</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="O10" t="s">
         <v>38</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="P10" t="s">
         <v>39</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="1" t="s">
+      <c r="Q10" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" t="s">
         <v>34</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="S10" t="s">
         <v>35</v>
       </c>
-      <c r="T10" s="1">
+      <c r="T10">
         <v>523</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>2023</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="P11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="Q11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="2">
         <v>15</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>36</v>
+      <c r="V11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>43</v>
+      </c>
+      <c r="R14" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" t="s">
+        <v>17</v>
+      </c>
+      <c r="T14" t="s">
+        <v>18</v>
+      </c>
+      <c r="U14" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" t="s">
+        <v>20</v>
+      </c>
+      <c r="W14" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2023</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" s="2">
+        <v>15</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16">
+        <v>2023</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>46</v>
+      </c>
+      <c r="R16" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" t="s">
+        <v>35</v>
+      </c>
+      <c r="T16">
+        <v>523</v>
+      </c>
+      <c r="V16" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2023</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" s="4">
+        <v>15</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1713,575 +2409,1101 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C289BB9-EE1E-4CA6-A663-FA147F2C4500}">
-  <dimension ref="A1:Y11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEFBCB1-7565-4FE0-B017-D3D3BD3EB63B}">
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="Q2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2023</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="2">
+        <v>15</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>2023</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4">
+        <v>523</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+      <c r="X4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T5" s="3">
+        <v>15</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G8" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H8" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I8" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J8" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K8" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L8" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M8" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N8" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O8" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" t="s">
+        <v>16</v>
+      </c>
+      <c r="S8" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" t="s">
+        <v>18</v>
+      </c>
+      <c r="U8" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" t="s">
+        <v>20</v>
+      </c>
+      <c r="W8" t="s">
+        <v>21</v>
+      </c>
+      <c r="X8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2023</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" s="2">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>2023</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T10">
+        <v>523</v>
+      </c>
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2023</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T11" s="2">
+        <v>15</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="R14" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S14" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T14" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U14" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V14" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W14" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X14" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="15" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F15" s="2">
         <v>2023</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="3" t="s">
+      <c r="P15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" s="2">
+        <v>15</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16">
+        <v>2023</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>47</v>
+      </c>
+      <c r="R16" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" t="s">
+        <v>35</v>
+      </c>
+      <c r="T16">
+        <v>523</v>
+      </c>
+      <c r="V16" t="s">
+        <v>36</v>
+      </c>
+      <c r="W16" t="s">
+        <v>36</v>
+      </c>
+      <c r="X16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2023</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" s="4">
+        <v>15</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" s="3">
-        <v>15</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" s="1">
-        <v>523</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4">
-        <v>2023</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" s="4">
-        <v>15</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>2</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T9" s="1">
-        <v>15</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="N22" t="s">
+        <v>55</v>
+      </c>
+      <c r="P22" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T10" s="1">
-        <v>523</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T11" s="1">
-        <v>15</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>36</v>
+      <c r="Q22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="P23" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2f73c15ba4091178a7f0362f23ea5149">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a657112-7d30-43e0-84e9-071e428c6b63" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec4077129998c06208654d7e46c796ff" ns2:_="">
+    <xsd:import namespace="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a657112-7d30-43e0-84e9-071e428c6b63" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E5A1299-5656-415E-9580-483843D50238}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D470FC-AF33-4BA1-8CBA-D216B1974BAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD55C9A-33CD-4E1A-9CA4-9853FDD2BDEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" enabled="0" method="" siteId="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/WGRDBESstockCoord/format/CEF_issues/counts_mandatory.xlsx
+++ b/WGRDBESstockCoord/format/CEF_issues/counts_mandatory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/CEF_issues/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{E02EFAED-1830-484F-A16C-64F57909150A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE06C13B-299A-4E38-A818-4C383D185A03}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{E02EFAED-1830-484F-A16C-64F57909150A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA0C3EDB-600D-4557-9B03-66AB728882D8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{E9EDB1D5-AC8B-401D-A7AA-35A6E4ABEA11}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E9EDB1D5-AC8B-401D-A7AA-35A6E4ABEA11}"/>
   </bookViews>
   <sheets>
     <sheet name="dataBasis" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="62">
   <si>
     <t>no</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>This could work, but is will require changes in the upload facilities and functions</t>
+  </si>
+  <si>
+    <t>NotApplicable</t>
   </si>
 </sst>
 </file>
@@ -380,9 +383,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>292285</xdr:colOff>
+      <xdr:colOff>288475</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>133738</xdr:rowOff>
+      <xdr:rowOff>129928</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2828,7 +2831,7 @@
         <v>32</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>46</v>
@@ -2893,7 +2896,7 @@
         <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="s">
         <v>47</v>
@@ -2955,7 +2958,7 @@
         <v>38</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>47</v>
@@ -3446,18 +3449,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3479,14 +3482,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D470FC-AF33-4BA1-8CBA-D216B1974BAC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD55C9A-33CD-4E1A-9CA4-9853FDD2BDEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3502,6 +3497,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D470FC-AF33-4BA1-8CBA-D216B1974BAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" enabled="0" method="" siteId="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" removed="1"/>
